--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_27-02-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_27-02-2026.xlsx
@@ -941,7 +941,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>£21.12</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>£21.36</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /60mm_celotex_ga4000_pir_insulation.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x0000014735DCE450&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=30)'))</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>£19.67</t>
+          <t>Error: HTTPSConnectionPool(host='www.tradeinsulations.co.uk', port=443): Max retries exceeded with url: /product/60mm-celotex/ (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x00000147331F41D0&gt;, 'Connection to www.tradeinsulations.co.uk timed out. (connect timeout=30)'))</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>£22.95</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/celotex-70mm-ga4070-insulation-board-2-4m-x-1-2m-17.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x00000147362DB110&gt;, 'Connection to www.insulationsuperstore.co.uk timed out. (connect timeout=30)'))</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>£22.05</t>
+          <t>Error: HTTPSConnectionPool(host='onlineinsulation-sales.com', port=443): Max retries exceeded with url: /70mm-celotex-ga4070-pir-insulation-board-2400x1200mm-709-p.asp (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x0000014734014A90&gt;, 'Connection to onlineinsulation-sales.com timed out. (connect timeout=30)'))</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>£23.13</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /70mm_celotex_ga4000_pir_insulation.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x0000014733096590&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=30)'))</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>£22.05</t>
+          <t>Error: HTTPSConnectionPool(host='www.tradeinsulations.co.uk', port=443): Max retries exceeded with url: /product/70mm-celotex/ (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x00000147330F7B50&gt;, 'Connection to www.tradeinsulations.co.uk timed out. (connect timeout=30)'))</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>£22.10</t>
+          <t>Error: HTTPSConnectionPool(host='onlineinsulation-sales.com', port=443): Max retries exceeded with url: /75mm-celotex-ga4075-pir-insulation-board-2400x1200mm-11-p.asp (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x00000147368A6D50&gt;, 'Connection to onlineinsulation-sales.com timed out. (connect timeout=30)'))</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
